--- a/98 - Excels/Open-LPs - deitado.xlsx
+++ b/98 - Excels/Open-LPs - deitado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3AA41A-18CE-47ED-B185-9E18BDA2F515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FECDEDE-B4FB-4925-95D6-8671B3D26CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,174 +20,189 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-037756</t>
-  </si>
-  <si>
-    <t>LP-043172</t>
-  </si>
-  <si>
-    <t>LP-046472</t>
-  </si>
-  <si>
-    <t>LP-047850</t>
-  </si>
-  <si>
-    <t>LP-047995</t>
-  </si>
-  <si>
-    <t>LP-048318</t>
-  </si>
-  <si>
-    <t>LP-048321</t>
-  </si>
-  <si>
-    <t>LP-050394</t>
-  </si>
-  <si>
-    <t>LP-050480</t>
-  </si>
-  <si>
-    <t>LP-050592</t>
-  </si>
-  <si>
-    <t>LP-051045</t>
-  </si>
-  <si>
-    <t>LP-051127</t>
-  </si>
-  <si>
-    <t>LP-051410</t>
-  </si>
-  <si>
-    <t>LP-051441</t>
-  </si>
-  <si>
-    <t>LP-051496</t>
-  </si>
-  <si>
-    <t>LP-051515</t>
-  </si>
-  <si>
-    <t>LP-051547</t>
-  </si>
-  <si>
-    <t>LP-051590</t>
-  </si>
-  <si>
-    <t>LP-051773</t>
-  </si>
-  <si>
-    <t>LP-051896</t>
-  </si>
-  <si>
-    <t>LP-051897</t>
-  </si>
-  <si>
-    <t>LP-051898</t>
-  </si>
-  <si>
-    <t>LP-051920</t>
-  </si>
-  <si>
-    <t>LP-051921</t>
-  </si>
-  <si>
-    <t>LP-052027</t>
-  </si>
-  <si>
-    <t>LP-052033</t>
-  </si>
-  <si>
-    <t>LP-052143</t>
-  </si>
-  <si>
-    <t>LP-052144</t>
-  </si>
-  <si>
-    <t>LP-052305</t>
-  </si>
-  <si>
-    <t>LP-052425</t>
-  </si>
-  <si>
-    <t>LP-052428</t>
-  </si>
-  <si>
-    <t>LP-052565</t>
-  </si>
-  <si>
-    <t>LP-052566</t>
-  </si>
-  <si>
-    <t>LP-052567</t>
-  </si>
-  <si>
-    <t>LP-052582</t>
-  </si>
-  <si>
-    <t>LP-052593</t>
-  </si>
-  <si>
-    <t>LP-052594</t>
-  </si>
-  <si>
-    <t>LP-052605</t>
-  </si>
-  <si>
-    <t>LP-052606</t>
-  </si>
-  <si>
-    <t>LP-052607</t>
-  </si>
-  <si>
-    <t>LP-052638</t>
-  </si>
-  <si>
-    <t>LP-052673</t>
-  </si>
-  <si>
-    <t>LP-052685</t>
-  </si>
-  <si>
-    <t>LP-052686</t>
-  </si>
-  <si>
-    <t>LP-052718</t>
-  </si>
-  <si>
-    <t>LP-052777</t>
-  </si>
-  <si>
-    <t>LP-052824</t>
-  </si>
-  <si>
-    <t>LP-053000</t>
-  </si>
-  <si>
-    <t>LP-053131</t>
-  </si>
-  <si>
-    <t>LP-053150</t>
-  </si>
-  <si>
-    <t>LP-053166</t>
-  </si>
-  <si>
-    <t>LP-053279</t>
-  </si>
-  <si>
-    <t>LP-052532</t>
-  </si>
-  <si>
-    <t>LP-052688</t>
-  </si>
-  <si>
-    <t>LP-052927</t>
+    <t>LP-034807</t>
+  </si>
+  <si>
+    <t>LP-047231</t>
+  </si>
+  <si>
+    <t>LP-050005</t>
+  </si>
+  <si>
+    <t>LP-051088</t>
+  </si>
+  <si>
+    <t>LP-051089</t>
+  </si>
+  <si>
+    <t>LP-051757</t>
+  </si>
+  <si>
+    <t>LP-051895</t>
+  </si>
+  <si>
+    <t>LP-051994</t>
+  </si>
+  <si>
+    <t>LP-052078</t>
+  </si>
+  <si>
+    <t>LP-052205</t>
+  </si>
+  <si>
+    <t>LP-052268</t>
+  </si>
+  <si>
+    <t>LP-052270</t>
+  </si>
+  <si>
+    <t>LP-052271</t>
+  </si>
+  <si>
+    <t>LP-052272</t>
+  </si>
+  <si>
+    <t>LP-052538</t>
+  </si>
+  <si>
+    <t>LP-052568</t>
+  </si>
+  <si>
+    <t>LP-052588</t>
+  </si>
+  <si>
+    <t>LP-052602</t>
+  </si>
+  <si>
+    <t>LP-052610</t>
+  </si>
+  <si>
+    <t>LP-052667</t>
+  </si>
+  <si>
+    <t>LP-052692</t>
+  </si>
+  <si>
+    <t>LP-052742</t>
+  </si>
+  <si>
+    <t>LP-052762</t>
+  </si>
+  <si>
+    <t>LP-052776</t>
+  </si>
+  <si>
+    <t>LP-052778</t>
+  </si>
+  <si>
+    <t>LP-052811</t>
+  </si>
+  <si>
+    <t>LP-052832</t>
+  </si>
+  <si>
+    <t>LP-052834</t>
+  </si>
+  <si>
+    <t>LP-052840</t>
+  </si>
+  <si>
+    <t>LP-052846</t>
+  </si>
+  <si>
+    <t>LP-052849</t>
+  </si>
+  <si>
+    <t>LP-052883</t>
+  </si>
+  <si>
+    <t>LP-052926</t>
+  </si>
+  <si>
+    <t>LP-052948</t>
+  </si>
+  <si>
+    <t>LP-053183</t>
+  </si>
+  <si>
+    <t>LP-053190</t>
+  </si>
+  <si>
+    <t>LP-053285</t>
+  </si>
+  <si>
+    <t>LP-053287</t>
+  </si>
+  <si>
+    <t>LP-053288</t>
+  </si>
+  <si>
+    <t>LP-053360</t>
+  </si>
+  <si>
+    <t>LP-053462</t>
+  </si>
+  <si>
+    <t>LP-053661</t>
+  </si>
+  <si>
+    <t>LP-053710</t>
+  </si>
+  <si>
+    <t>LP-053795</t>
+  </si>
+  <si>
+    <t>LP-053813</t>
+  </si>
+  <si>
+    <t>LP-053820</t>
+  </si>
+  <si>
+    <t>LP-053823</t>
+  </si>
+  <si>
+    <t>LP-053841</t>
+  </si>
+  <si>
+    <t>LP-053864</t>
+  </si>
+  <si>
+    <t>LP-047283</t>
+  </si>
+  <si>
+    <t>LP-048855</t>
+  </si>
+  <si>
+    <t>LP-052590</t>
+  </si>
+  <si>
+    <t>LP-052835</t>
+  </si>
+  <si>
+    <t>LP-052886</t>
+  </si>
+  <si>
+    <t>LP-053525</t>
+  </si>
+  <si>
+    <t>LP-053605</t>
+  </si>
+  <si>
+    <t>LP-053652</t>
+  </si>
+  <si>
+    <t>LP-053815</t>
+  </si>
+  <si>
+    <t>LP-053857</t>
+  </si>
+  <si>
+    <t>LP-053858</t>
   </si>
 </sst>
 </file>
@@ -550,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -573,147 +588,147 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -723,127 +738,142 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs - deitado.xlsx
+++ b/98 - Excels/Open-LPs - deitado.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EF5F14-6DD5-4C68-B6A3-1D5779A6E0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9426BB1-ED76-4C77-A43A-A259B2B4B3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,153 +20,255 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-039750</t>
-  </si>
-  <si>
-    <t>LP-046498</t>
-  </si>
-  <si>
-    <t>LP-047046</t>
-  </si>
-  <si>
-    <t>LP-047223</t>
-  </si>
-  <si>
-    <t>LP-047760</t>
-  </si>
-  <si>
-    <t>LP-049191</t>
-  </si>
-  <si>
-    <t>LP-050532</t>
-  </si>
-  <si>
-    <t>LP-050560</t>
-  </si>
-  <si>
-    <t>LP-050651</t>
-  </si>
-  <si>
-    <t>LP-050801</t>
-  </si>
-  <si>
-    <t>LP-050851</t>
-  </si>
-  <si>
-    <t>LP-050852</t>
-  </si>
-  <si>
-    <t>LP-050931</t>
-  </si>
-  <si>
-    <t>LP-051561</t>
-  </si>
-  <si>
-    <t>LP-051598</t>
-  </si>
-  <si>
-    <t>LP-051696</t>
-  </si>
-  <si>
-    <t>LP-051928</t>
-  </si>
-  <si>
-    <t>LP-051962</t>
-  </si>
-  <si>
-    <t>LP-052073</t>
-  </si>
-  <si>
-    <t>LP-052077</t>
+    <t>LP-047465</t>
+  </si>
+  <si>
+    <t>LP-048897</t>
+  </si>
+  <si>
+    <t>LP-049755</t>
+  </si>
+  <si>
+    <t>LP-049885</t>
+  </si>
+  <si>
+    <t>LP-050304</t>
+  </si>
+  <si>
+    <t>LP-050763</t>
+  </si>
+  <si>
+    <t>LP-051074</t>
+  </si>
+  <si>
+    <t>LP-051442</t>
+  </si>
+  <si>
+    <t>LP-051657</t>
+  </si>
+  <si>
+    <t>LP-051661</t>
+  </si>
+  <si>
+    <t>LP-051698</t>
+  </si>
+  <si>
+    <t>LP-051755</t>
+  </si>
+  <si>
+    <t>LP-051984</t>
   </si>
   <si>
     <t>LP-052191</t>
   </si>
   <si>
-    <t>LP-052269</t>
-  </si>
-  <si>
-    <t>LP-052297</t>
-  </si>
-  <si>
-    <t>LP-052346</t>
-  </si>
-  <si>
-    <t>LP-052390</t>
-  </si>
-  <si>
-    <t>LP-052393</t>
-  </si>
-  <si>
-    <t>LP-052427</t>
-  </si>
-  <si>
-    <t>LP-052471</t>
-  </si>
-  <si>
-    <t>LP-052573</t>
-  </si>
-  <si>
-    <t>LP-052608</t>
-  </si>
-  <si>
-    <t>LP-052637</t>
-  </si>
-  <si>
-    <t>LP-052657</t>
-  </si>
-  <si>
-    <t>LP-052687</t>
-  </si>
-  <si>
-    <t>LP-052757</t>
-  </si>
-  <si>
-    <t>LP-052851</t>
-  </si>
-  <si>
-    <t>LP-052859</t>
-  </si>
-  <si>
-    <t>LP-052974</t>
-  </si>
-  <si>
-    <t>LP-053134</t>
-  </si>
-  <si>
-    <t>LP-053140</t>
-  </si>
-  <si>
-    <t>LP-053333</t>
-  </si>
-  <si>
-    <t>LP-053366</t>
-  </si>
-  <si>
-    <t>LP-053536</t>
-  </si>
-  <si>
-    <t>LP-053641</t>
-  </si>
-  <si>
-    <t>LP-049077</t>
-  </si>
-  <si>
-    <t>LP-052059</t>
-  </si>
-  <si>
-    <t>LP-052764</t>
-  </si>
-  <si>
-    <t>LP-052850</t>
-  </si>
-  <si>
-    <t>LP-053646</t>
+    <t>LP-052193</t>
+  </si>
+  <si>
+    <t>LP-052539</t>
+  </si>
+  <si>
+    <t>LP-052557</t>
+  </si>
+  <si>
+    <t>LP-052558</t>
+  </si>
+  <si>
+    <t>LP-052561</t>
+  </si>
+  <si>
+    <t>LP-052563</t>
+  </si>
+  <si>
+    <t>LP-052639</t>
+  </si>
+  <si>
+    <t>LP-052641</t>
+  </si>
+  <si>
+    <t>LP-052659</t>
+  </si>
+  <si>
+    <t>LP-052665</t>
+  </si>
+  <si>
+    <t>LP-052715</t>
+  </si>
+  <si>
+    <t>LP-052743</t>
+  </si>
+  <si>
+    <t>LP-052763</t>
+  </si>
+  <si>
+    <t>LP-052775</t>
+  </si>
+  <si>
+    <t>LP-052795</t>
+  </si>
+  <si>
+    <t>LP-052845</t>
+  </si>
+  <si>
+    <t>LP-052892</t>
+  </si>
+  <si>
+    <t>LP-052911</t>
+  </si>
+  <si>
+    <t>LP-052968</t>
+  </si>
+  <si>
+    <t>LP-052998</t>
+  </si>
+  <si>
+    <t>LP-053043</t>
+  </si>
+  <si>
+    <t>LP-053088</t>
+  </si>
+  <si>
+    <t>LP-053141</t>
+  </si>
+  <si>
+    <t>LP-053152</t>
+  </si>
+  <si>
+    <t>LP-053202</t>
+  </si>
+  <si>
+    <t>LP-053269</t>
+  </si>
+  <si>
+    <t>LP-053273</t>
+  </si>
+  <si>
+    <t>LP-053274</t>
+  </si>
+  <si>
+    <t>LP-053282</t>
+  </si>
+  <si>
+    <t>LP-053284</t>
+  </si>
+  <si>
+    <t>LP-053323</t>
+  </si>
+  <si>
+    <t>LP-053334</t>
+  </si>
+  <si>
+    <t>LP-053347</t>
+  </si>
+  <si>
+    <t>LP-053355</t>
+  </si>
+  <si>
+    <t>LP-053358</t>
+  </si>
+  <si>
+    <t>LP-053359</t>
+  </si>
+  <si>
+    <t>LP-053367</t>
+  </si>
+  <si>
+    <t>LP-053368</t>
+  </si>
+  <si>
+    <t>LP-053520</t>
+  </si>
+  <si>
+    <t>LP-053581</t>
+  </si>
+  <si>
+    <t>LP-053582</t>
+  </si>
+  <si>
+    <t>LP-053583</t>
+  </si>
+  <si>
+    <t>LP-053584</t>
+  </si>
+  <si>
+    <t>LP-053585</t>
+  </si>
+  <si>
+    <t>LP-053664</t>
+  </si>
+  <si>
+    <t>LP-053666</t>
+  </si>
+  <si>
+    <t>LP-053667</t>
+  </si>
+  <si>
+    <t>LP-053706</t>
+  </si>
+  <si>
+    <t>LP-053716</t>
+  </si>
+  <si>
+    <t>LP-053784</t>
+  </si>
+  <si>
+    <t>LP-053785</t>
+  </si>
+  <si>
+    <t>LP-053788</t>
+  </si>
+  <si>
+    <t>LP-053811</t>
+  </si>
+  <si>
+    <t>LP-053812</t>
+  </si>
+  <si>
+    <t>LP-053874</t>
+  </si>
+  <si>
+    <t>LP-053876</t>
+  </si>
+  <si>
+    <t>LP-053877</t>
+  </si>
+  <si>
+    <t>LP-053967</t>
+  </si>
+  <si>
+    <t>LP-053993</t>
+  </si>
+  <si>
+    <t>LP-054057</t>
+  </si>
+  <si>
+    <t>LP-054058</t>
+  </si>
+  <si>
+    <t>LP-054059</t>
+  </si>
+  <si>
+    <t>LP-054076</t>
+  </si>
+  <si>
+    <t>LP-054201</t>
+  </si>
+  <si>
+    <t>LP-054205</t>
+  </si>
+  <si>
+    <t>LP-054219</t>
+  </si>
+  <si>
+    <t>LP-054087</t>
+  </si>
+  <si>
+    <t>LP-052761</t>
   </si>
 </sst>
 </file>
@@ -529,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -567,222 +669,387 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/98 - Excels/Open-LPs - deitado.xlsx
+++ b/98 - Excels/Open-LPs - deitado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9426BB1-ED76-4C77-A43A-A259B2B4B3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CBABFB-FF3D-408E-9FAC-86EEC7A67176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,255 +20,156 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-047465</t>
-  </si>
-  <si>
-    <t>LP-048897</t>
-  </si>
-  <si>
-    <t>LP-049755</t>
-  </si>
-  <si>
-    <t>LP-049885</t>
-  </si>
-  <si>
-    <t>LP-050304</t>
-  </si>
-  <si>
-    <t>LP-050763</t>
-  </si>
-  <si>
-    <t>LP-051074</t>
-  </si>
-  <si>
-    <t>LP-051442</t>
-  </si>
-  <si>
-    <t>LP-051657</t>
-  </si>
-  <si>
-    <t>LP-051661</t>
-  </si>
-  <si>
-    <t>LP-051698</t>
-  </si>
-  <si>
-    <t>LP-051755</t>
-  </si>
-  <si>
-    <t>LP-051984</t>
-  </si>
-  <si>
-    <t>LP-052191</t>
-  </si>
-  <si>
-    <t>LP-052193</t>
-  </si>
-  <si>
-    <t>LP-052539</t>
-  </si>
-  <si>
-    <t>LP-052557</t>
-  </si>
-  <si>
-    <t>LP-052558</t>
-  </si>
-  <si>
-    <t>LP-052561</t>
-  </si>
-  <si>
-    <t>LP-052563</t>
-  </si>
-  <si>
-    <t>LP-052639</t>
-  </si>
-  <si>
-    <t>LP-052641</t>
-  </si>
-  <si>
-    <t>LP-052659</t>
-  </si>
-  <si>
-    <t>LP-052665</t>
-  </si>
-  <si>
-    <t>LP-052715</t>
-  </si>
-  <si>
-    <t>LP-052743</t>
-  </si>
-  <si>
-    <t>LP-052763</t>
-  </si>
-  <si>
-    <t>LP-052775</t>
-  </si>
-  <si>
-    <t>LP-052795</t>
-  </si>
-  <si>
-    <t>LP-052845</t>
-  </si>
-  <si>
-    <t>LP-052892</t>
-  </si>
-  <si>
-    <t>LP-052911</t>
-  </si>
-  <si>
-    <t>LP-052968</t>
-  </si>
-  <si>
-    <t>LP-052998</t>
-  </si>
-  <si>
-    <t>LP-053043</t>
-  </si>
-  <si>
-    <t>LP-053088</t>
-  </si>
-  <si>
-    <t>LP-053141</t>
-  </si>
-  <si>
-    <t>LP-053152</t>
-  </si>
-  <si>
-    <t>LP-053202</t>
-  </si>
-  <si>
-    <t>LP-053269</t>
-  </si>
-  <si>
-    <t>LP-053273</t>
-  </si>
-  <si>
-    <t>LP-053274</t>
-  </si>
-  <si>
-    <t>LP-053282</t>
-  </si>
-  <si>
-    <t>LP-053284</t>
-  </si>
-  <si>
-    <t>LP-053323</t>
-  </si>
-  <si>
-    <t>LP-053334</t>
-  </si>
-  <si>
-    <t>LP-053347</t>
-  </si>
-  <si>
-    <t>LP-053355</t>
-  </si>
-  <si>
-    <t>LP-053358</t>
-  </si>
-  <si>
-    <t>LP-053359</t>
-  </si>
-  <si>
-    <t>LP-053367</t>
-  </si>
-  <si>
-    <t>LP-053368</t>
-  </si>
-  <si>
-    <t>LP-053520</t>
-  </si>
-  <si>
-    <t>LP-053581</t>
-  </si>
-  <si>
-    <t>LP-053582</t>
-  </si>
-  <si>
-    <t>LP-053583</t>
-  </si>
-  <si>
-    <t>LP-053584</t>
-  </si>
-  <si>
-    <t>LP-053585</t>
-  </si>
-  <si>
-    <t>LP-053664</t>
-  </si>
-  <si>
-    <t>LP-053666</t>
-  </si>
-  <si>
-    <t>LP-053667</t>
-  </si>
-  <si>
-    <t>LP-053706</t>
-  </si>
-  <si>
-    <t>LP-053716</t>
-  </si>
-  <si>
-    <t>LP-053784</t>
-  </si>
-  <si>
-    <t>LP-053785</t>
-  </si>
-  <si>
-    <t>LP-053788</t>
-  </si>
-  <si>
-    <t>LP-053811</t>
-  </si>
-  <si>
-    <t>LP-053812</t>
-  </si>
-  <si>
-    <t>LP-053874</t>
-  </si>
-  <si>
-    <t>LP-053876</t>
-  </si>
-  <si>
-    <t>LP-053877</t>
-  </si>
-  <si>
-    <t>LP-053967</t>
-  </si>
-  <si>
-    <t>LP-053993</t>
-  </si>
-  <si>
-    <t>LP-054057</t>
-  </si>
-  <si>
-    <t>LP-054058</t>
-  </si>
-  <si>
-    <t>LP-054059</t>
-  </si>
-  <si>
-    <t>LP-054076</t>
-  </si>
-  <si>
-    <t>LP-054201</t>
-  </si>
-  <si>
-    <t>LP-054205</t>
-  </si>
-  <si>
-    <t>LP-054219</t>
-  </si>
-  <si>
-    <t>LP-054087</t>
-  </si>
-  <si>
-    <t>LP-052761</t>
+    <t>LP-051120</t>
+  </si>
+  <si>
+    <t>LP-051764</t>
+  </si>
+  <si>
+    <t>LP-052147</t>
+  </si>
+  <si>
+    <t>LP-052415</t>
+  </si>
+  <si>
+    <t>LP-052666</t>
+  </si>
+  <si>
+    <t>LP-052813</t>
+  </si>
+  <si>
+    <t>LP-052965</t>
+  </si>
+  <si>
+    <t>LP-053169</t>
+  </si>
+  <si>
+    <t>LP-053369</t>
+  </si>
+  <si>
+    <t>LP-053476</t>
+  </si>
+  <si>
+    <t>LP-053481</t>
+  </si>
+  <si>
+    <t>LP-053547</t>
+  </si>
+  <si>
+    <t>LP-053548</t>
+  </si>
+  <si>
+    <t>LP-053549</t>
+  </si>
+  <si>
+    <t>LP-053576</t>
+  </si>
+  <si>
+    <t>LP-053579</t>
+  </si>
+  <si>
+    <t>LP-053580</t>
+  </si>
+  <si>
+    <t>LP-053586</t>
+  </si>
+  <si>
+    <t>LP-053612</t>
+  </si>
+  <si>
+    <t>LP-053632</t>
+  </si>
+  <si>
+    <t>LP-053745</t>
+  </si>
+  <si>
+    <t>LP-053790</t>
+  </si>
+  <si>
+    <t>LP-053791</t>
+  </si>
+  <si>
+    <t>LP-053792</t>
+  </si>
+  <si>
+    <t>LP-053793</t>
+  </si>
+  <si>
+    <t>LP-053978</t>
+  </si>
+  <si>
+    <t>LP-054039</t>
+  </si>
+  <si>
+    <t>LP-054138</t>
+  </si>
+  <si>
+    <t>LP-054142</t>
+  </si>
+  <si>
+    <t>LP-054143</t>
+  </si>
+  <si>
+    <t>LP-054146</t>
+  </si>
+  <si>
+    <t>LP-054223</t>
+  </si>
+  <si>
+    <t>LP-054271</t>
+  </si>
+  <si>
+    <t>LP-054279</t>
+  </si>
+  <si>
+    <t>LP-054281</t>
+  </si>
+  <si>
+    <t>LP-054284</t>
+  </si>
+  <si>
+    <t>LP-054285</t>
+  </si>
+  <si>
+    <t>LP-054516</t>
+  </si>
+  <si>
+    <t>LP-054522</t>
+  </si>
+  <si>
+    <t>LP-054523</t>
+  </si>
+  <si>
+    <t>LP-054526</t>
+  </si>
+  <si>
+    <t>LP-054567</t>
+  </si>
+  <si>
+    <t>LP-054583</t>
+  </si>
+  <si>
+    <t>LP-054641</t>
+  </si>
+  <si>
+    <t>LP-054644</t>
+  </si>
+  <si>
+    <t>LP-054657</t>
+  </si>
+  <si>
+    <t>LP-054699</t>
+  </si>
+  <si>
+    <t>LP-054713</t>
+  </si>
+  <si>
+    <t>LP-054141</t>
   </si>
 </sst>
 </file>
@@ -631,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A83"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -774,17 +675,17 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
@@ -874,182 +775,22 @@
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
